--- a/reports/集团总公司_现金流量表_2025-08.xlsx
+++ b/reports/集团总公司_现金流量表_2025-08.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>218400000</v>
+        <v>217957197</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1571700000</v>
+        <v>1571651302</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4505481</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>32324578</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2235321</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>16147697</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1128099</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>8084823</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>893617</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>6457053</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>676547</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>4851562</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>447459</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3228693</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>337505</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2425210</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>224374</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1614982</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>560733</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>4039951</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>282788</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2030251</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>177792</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1283752</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>593600</v>
+        <v>596336</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4271800</v>
+        <v>4274589</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>4032000</v>
+        <v>4011893</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>29016000</v>
+        <v>28992047</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>223025600</v>
+        <v>234035142</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>134400000</v>
+        <v>134413210</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>967200000</v>
+        <v>967549251</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1499017</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>10770606</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1119269</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>8076727</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>751437</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>5388366</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>558600</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>4036368</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>376062</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>2695174</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>280762</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2028124</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>27104000</v>
+        <v>27209122</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>195052000</v>
+        <v>195223419</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>12544000</v>
+        <v>12510523</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>90272000</v>
+        <v>90204622</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5712000</v>
+        <v>5718740</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>41106000</v>
+        <v>41128030</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>179760000</v>
+        <v>184436742</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>43265600</v>
+        <v>49598400</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>241073</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1920000</v>
+        <v>1921782</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2104631</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>16800000</v>
+        <v>16810856</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1279157</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>10240000</v>
+        <v>10235969</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2345704</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>20049470</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>160000000</v>
+        <v>160032578</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2889180</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>23200000</v>
+        <v>23188717</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14265291</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>113600000</v>
+        <v>113681587</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>521626</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>4160000</v>
+        <v>4163242</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20571096</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18225392</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4686276</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>37600000</v>
+        <v>37588727</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7464147</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>60000000</v>
+        <v>59953276</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7537485</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>60000000</v>
+        <v>60054413</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>238874</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1920000</v>
+        <v>1918195</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12389297</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6083561</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>48800000</v>
+        <v>48764914</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6107382</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>48800000</v>
+        <v>48823785</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>1000400</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>8000000</v>
+        <v>7998362</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>872900</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>6960000</v>
+        <v>6962733</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>124457</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1000000</v>
+        <v>999357</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7208418</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5180879</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>30300600</v>
+        <v>36553887</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>30300600</v>
+        <v>36553887</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
